--- a/src/test/java/com/centralvista/testdata/pmotest.xlsx
+++ b/src/test/java/com/centralvista/testdata/pmotest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
   <si>
     <t>FullName</t>
   </si>
@@ -149,13 +149,73 @@
   </si>
   <si>
     <t>Recommender/Approver</t>
+  </si>
+  <si>
+    <t>pooja.singh@gmail.com</t>
+  </si>
+  <si>
+    <t>Sonal Singh</t>
+  </si>
+  <si>
+    <t>Priya  Singh</t>
+  </si>
+  <si>
+    <t>Ritiknathji Singh</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Tasha Singh</t>
+  </si>
+  <si>
+    <t>Bhsha Singh</t>
+  </si>
+  <si>
+    <t>Contact Number already exists.</t>
+  </si>
+  <si>
+    <t>zzzzzzz08@gmail.com</t>
+  </si>
+  <si>
+    <t>Aadhaar Card Number</t>
+  </si>
+  <si>
+    <t>:</t>
+  </si>
+  <si>
+    <t>Email already exists.</t>
+  </si>
+  <si>
+    <t>SPG10010</t>
+  </si>
+  <si>
+    <t>SPG10011</t>
+  </si>
+  <si>
+    <t>SPG10012</t>
+  </si>
+  <si>
+    <t>ID Number already exists.</t>
+  </si>
+  <si>
+    <t>pooja.singhhh@gmail.com</t>
+  </si>
+  <si>
+    <t>pooja.sing100@gmail.com</t>
+  </si>
+  <si>
+    <t>The provided Card/Force/SPG Number already exists for the category</t>
+  </si>
+  <si>
+    <t>spg no Singh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,13 +235,29 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0669C7"/>
+      <name val="Poppins Regular"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Poppins Regular"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -200,7 +276,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -220,13 +296,28 @@
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -531,10 +622,10 @@
     <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" style="15" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" customWidth="1"/>
-    <col min="8" max="8" width="23" style="11" customWidth="1"/>
-    <col min="9" max="9" width="15" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="18" customWidth="1"/>
+    <col min="9" max="9" width="15" style="18" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="24.42578125" bestFit="1" customWidth="1"/>
@@ -542,10 +633,10 @@
     <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.85546875" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="15" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="33.7109375" customWidth="1"/>
     <col min="19" max="19" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="15" customWidth="1"/>
     <col min="21" max="21" width="21.85546875" customWidth="1"/>
     <col min="22" max="22" width="20.42578125" customWidth="1"/>
   </cols>
@@ -566,16 +657,16 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -599,7 +690,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="13" t="s">
         <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
@@ -608,7 +699,7 @@
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="13" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -634,16 +725,16 @@
       <c r="E2" s="3">
         <v>26628</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="14" t="s">
         <v>28</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="17">
         <v>567823490123</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="17">
         <v>9876543217</v>
       </c>
       <c r="J2" s="2">
@@ -667,7 +758,7 @@
       <c r="P2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q2" s="19">
         <v>10008</v>
       </c>
       <c r="R2" s="2" t="s">
@@ -676,7 +767,7 @@
       <c r="S2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="19" t="s">
         <v>26</v>
       </c>
       <c r="U2" s="2" t="s">
@@ -686,17 +777,338 @@
         <v>42</v>
       </c>
     </row>
+    <row r="3" spans="1:22" ht="30">
+      <c r="A3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3">
+        <v>26628</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="17">
+        <v>567823490129</v>
+      </c>
+      <c r="I3" s="17">
+        <v>9876543217</v>
+      </c>
+      <c r="J3" s="2">
+        <v>9123456787</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="19">
+        <v>10009</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3">
+        <v>26628</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="17">
+        <v>567823490123</v>
+      </c>
+      <c r="I4" s="17">
+        <v>9779700979</v>
+      </c>
+      <c r="J4" s="2">
+        <v>9123456787</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>10010</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="30">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3">
+        <v>26628</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="17">
+        <v>567823490120</v>
+      </c>
+      <c r="I5" s="17">
+        <v>9899999990</v>
+      </c>
+      <c r="J5" s="2">
+        <v>9123456787</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>10011</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:22" ht="75">
+      <c r="A7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3">
+        <v>26628</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" s="17">
+        <v>900000000000</v>
+      </c>
+      <c r="I7" s="17">
+        <v>9899999101</v>
+      </c>
+      <c r="J7" s="2">
+        <v>9123456787</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>10019</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="18:18">
+      <c r="R17" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="18:18" ht="15.75">
+      <c r="R18" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="18:18" ht="15.75">
+      <c r="R19" s="10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="18:18" ht="15.75">
+      <c r="R20" s="10">
+        <v>56782300000000</v>
+      </c>
+    </row>
+    <row r="21" spans="18:18" ht="15.75">
+      <c r="R21" s="12">
+        <v>10008</v>
+      </c>
+    </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="12" t="s">
+      <c r="A55" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="12"/>
+      <c r="B55" s="9"/>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -715,10 +1127,10 @@
       <c r="B58" s="5"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -759,9 +1171,14 @@
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="B57" r:id="rId2"/>
     <hyperlink ref="B60" r:id="rId3"/>
+    <hyperlink ref="F3" r:id="rId4"/>
+    <hyperlink ref="F5" r:id="rId5"/>
+    <hyperlink ref="F4" r:id="rId6"/>
+    <hyperlink ref="R17" r:id="rId7"/>
+    <hyperlink ref="F7" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId9"/>
 </worksheet>
 </file>
 
